--- a/Модель покрытия.xlsx
+++ b/Модель покрытия.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programs\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904A420A-67E7-48F8-AB1B-142E48584C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD41394B-0F12-4EC5-93F1-0768EB6C8FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Исходник" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="312">
   <si>
     <t>District</t>
   </si>
@@ -533,9 +533,6 @@
     <t>Мирумян Давид</t>
   </si>
   <si>
-    <t>ASM North</t>
-  </si>
-  <si>
     <t>Милюков Андрей</t>
   </si>
   <si>
@@ -1106,9 +1103,6 @@
     <t>Республика Татарстан</t>
   </si>
   <si>
-    <t>HSR TATAR</t>
-  </si>
-  <si>
     <t>Архангельская область</t>
   </si>
   <si>
@@ -1128,6 +1122,12 @@
   </si>
   <si>
     <t>Канцтовары</t>
+  </si>
+  <si>
+    <t>DDM BASH</t>
+  </si>
+  <si>
+    <t>DDM Kamchatka</t>
   </si>
 </sst>
 </file>
@@ -2286,38 +2286,38 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -2346,13 +2346,10 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>303</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -2365,24 +2362,24 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3055,7 +3052,9 @@
       <c r="C2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E2" s="6" t="s">
         <v>76</v>
       </c>
@@ -3077,7 +3076,9 @@
       <c r="C3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E3" s="6" t="s">
         <v>79</v>
       </c>
@@ -3097,7 +3098,9 @@
       <c r="C4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E4" s="6" t="s">
         <v>81</v>
       </c>
@@ -3119,7 +3122,9 @@
       <c r="C5" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E5" s="6" t="s">
         <v>84</v>
       </c>
@@ -3139,7 +3144,9 @@
       <c r="C6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E6" s="6" t="s">
         <v>76</v>
       </c>
@@ -3159,7 +3166,9 @@
       <c r="C7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E7" s="6" t="s">
         <v>87</v>
       </c>
@@ -3179,7 +3188,9 @@
       <c r="C8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E8" s="6" t="s">
         <v>76</v>
       </c>
@@ -3199,7 +3210,9 @@
       <c r="C9" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E9" s="6" t="s">
         <v>87</v>
       </c>
@@ -3219,7 +3232,9 @@
       <c r="C10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E10" s="6" t="s">
         <v>87</v>
       </c>
@@ -3239,7 +3254,9 @@
       <c r="C11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E11" s="6" t="s">
         <v>92</v>
       </c>
@@ -3259,7 +3276,9 @@
       <c r="C12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E12" s="6" t="s">
         <v>92</v>
       </c>
@@ -3279,7 +3298,9 @@
       <c r="C13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E13" s="6" t="s">
         <v>92</v>
       </c>
@@ -3299,7 +3320,9 @@
       <c r="C14" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E14" s="6" t="s">
         <v>92</v>
       </c>
@@ -3496,14 +3519,14 @@
         <v>112</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H23" s="6"/>
     </row>
@@ -3512,20 +3535,20 @@
         <v>96</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H24" s="6"/>
     </row>
@@ -3534,20 +3557,20 @@
         <v>96</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H25" s="6"/>
     </row>
@@ -3556,20 +3579,20 @@
         <v>96</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H26" s="6"/>
     </row>
@@ -3578,20 +3601,20 @@
         <v>96</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H27" s="6"/>
     </row>
@@ -3600,20 +3623,20 @@
         <v>96</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H28" s="6"/>
     </row>
@@ -3622,20 +3645,20 @@
         <v>96</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H29" s="6"/>
     </row>
@@ -3644,20 +3667,20 @@
         <v>96</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H30" s="6"/>
     </row>
@@ -3666,1406 +3689,1545 @@
         <v>96</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="D32" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="6"/>
+        <v>129</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="6"/>
+        <v>129</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E37" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="D40" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" s="6"/>
+      <c r="D42" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H45" s="6"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H46" s="6"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D48" s="6"/>
+        <v>152</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E48" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D49" s="6"/>
+        <v>152</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E49" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H49" s="6"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D50" s="6"/>
+        <v>152</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E50" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H50" s="6"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H51" s="6"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="D52" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H52" s="6"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H53" s="6"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H54" s="6"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D55" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E55" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H55" s="6"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B56" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H56" s="6"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H57" s="6"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D58" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E58" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H58" s="6"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B59" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="D59" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H59" s="6"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B60" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H60" s="6"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="D61" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B62" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H62" s="6"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H63" s="6"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="D64" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H64" s="6"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B66" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H66" s="6"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D67" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E67" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C68" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C70" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B71" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D72" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E72" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D73" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E73" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H73" s="6"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="C74" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="D74" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E74" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H74" s="6"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C75" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E75" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H75" s="6"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C76" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H76" s="6"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C77" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E77" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H77" s="6"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C78" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H78" s="6"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B79" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H79" s="6"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D80" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E80" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H80" s="6"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D81" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E81" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H81" s="6"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E82" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H82" s="6"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D83" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E83" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H83" s="6"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D84" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E84" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H84" s="6"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B85" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="D85" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E85" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H85" s="6"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B86" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E86" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D87" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E87" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H87" s="6"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D88" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E88" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H88" s="6"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D89" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E89" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H89" s="6"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D90" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E90" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H90" s="6"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D91" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E91" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H91" s="6"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="D92" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E92" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C93" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E93" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C94" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E94" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H94" s="6"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C95" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E95" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H95" s="6"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D96" s="6"/>
+        <v>237</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E96" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H96" s="6"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B97" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E97" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H97" s="6"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D98" s="6"/>
+        <v>237</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E98" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F98" s="6"/>
       <c r="G98" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H98" s="6"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D99" s="6"/>
+        <v>237</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="E99" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F99" s="6"/>
       <c r="G99" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H99" s="6"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B100" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="F100" s="6"/>
       <c r="G100" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H100" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I100" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5103,7 +5265,7 @@
         <v>72</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -5111,20 +5273,20 @@
         <v>73</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5132,20 +5294,20 @@
         <v>73</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="D3" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
         <v>78</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -5153,20 +5315,20 @@
         <v>73</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -5174,20 +5336,20 @@
         <v>73</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -5195,388 +5357,388 @@
         <v>73</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>273</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D13" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D14" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="D23" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">

--- a/Модель покрытия.xlsx
+++ b/Модель покрытия.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programs\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD41394B-0F12-4EC5-93F1-0768EB6C8FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD44CD54-76BA-4E40-805C-7D0A678E2E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Исходник" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -192,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="395">
   <si>
     <t>District</t>
   </si>
@@ -1124,10 +1122,259 @@
     <t>Канцтовары</t>
   </si>
   <si>
-    <t>DDM BASH</t>
-  </si>
-  <si>
     <t>DDM Kamchatka</t>
+  </si>
+  <si>
+    <t>Дистр(?)</t>
+  </si>
+  <si>
+    <t>Республика Башкортостан</t>
+  </si>
+  <si>
+    <t>HSR BASH</t>
+  </si>
+  <si>
+    <t>TDM BASH</t>
+  </si>
+  <si>
+    <t>RAE BASH</t>
+  </si>
+  <si>
+    <t>RAE BASH 2</t>
+  </si>
+  <si>
+    <t>RAE BASH 3</t>
+  </si>
+  <si>
+    <t>TDM BASH 2</t>
+  </si>
+  <si>
+    <t>TDM BASH 3</t>
+  </si>
+  <si>
+    <t>TDM CHEL</t>
+  </si>
+  <si>
+    <t>TDM CHEL 2</t>
+  </si>
+  <si>
+    <t>TDM CHEL 3</t>
+  </si>
+  <si>
+    <t>RAEBASH 4</t>
+  </si>
+  <si>
+    <t>RAE CHEL</t>
+  </si>
+  <si>
+    <t>RAE CHEL 2</t>
+  </si>
+  <si>
+    <t>RAE CHEL 3</t>
+  </si>
+  <si>
+    <t>RAE CHEL 4</t>
+  </si>
+  <si>
+    <t>HSR CHEL</t>
+  </si>
+  <si>
+    <t>DDM TUL</t>
+  </si>
+  <si>
+    <t>DDM RYAZ</t>
+  </si>
+  <si>
+    <t>DDM KALYJ</t>
+  </si>
+  <si>
+    <t>DDM Nish</t>
+  </si>
+  <si>
+    <t>DDM Vladim</t>
+  </si>
+  <si>
+    <t>DDM Chyvash</t>
+  </si>
+  <si>
+    <t>DDM Kirov</t>
+  </si>
+  <si>
+    <t>DDM MARIYEL</t>
+  </si>
+  <si>
+    <t>DDM MORD</t>
+  </si>
+  <si>
+    <t>DDM PITER</t>
+  </si>
+  <si>
+    <t>DDM MURM</t>
+  </si>
+  <si>
+    <t>DDM NOVG</t>
+  </si>
+  <si>
+    <t>DDM KAREL</t>
+  </si>
+  <si>
+    <t>DDM PSKOV</t>
+  </si>
+  <si>
+    <t>DDM KALINING</t>
+  </si>
+  <si>
+    <t>DDM KOMI</t>
+  </si>
+  <si>
+    <t>DDM NENEC</t>
+  </si>
+  <si>
+    <t>DDM VOLOGOD</t>
+  </si>
+  <si>
+    <t>DDM ARHANG</t>
+  </si>
+  <si>
+    <t>DDM YAROSL</t>
+  </si>
+  <si>
+    <t>DDM KOSTROM</t>
+  </si>
+  <si>
+    <t>DDM TVER</t>
+  </si>
+  <si>
+    <t>DDM IVAN</t>
+  </si>
+  <si>
+    <t>DDM SMOLENSK</t>
+  </si>
+  <si>
+    <t>DDM SAXAL</t>
+  </si>
+  <si>
+    <t>DDM MAGADAN</t>
+  </si>
+  <si>
+    <t>DDM PRIMORSK</t>
+  </si>
+  <si>
+    <t>DDM PRMORSK</t>
+  </si>
+  <si>
+    <t>DDM XABAR</t>
+  </si>
+  <si>
+    <t>DDM EVREY</t>
+  </si>
+  <si>
+    <t>DDM YAKUT</t>
+  </si>
+  <si>
+    <t>DDM AMUR</t>
+  </si>
+  <si>
+    <t>DDM SABAYK</t>
+  </si>
+  <si>
+    <t>DDM BYRAT</t>
+  </si>
+  <si>
+    <t>DDM IRKUTSK</t>
+  </si>
+  <si>
+    <t>DDM TATAR</t>
+  </si>
+  <si>
+    <t>DDM BASHK</t>
+  </si>
+  <si>
+    <t>DDM UDMU</t>
+  </si>
+  <si>
+    <t>DDM PERM</t>
+  </si>
+  <si>
+    <t>DDM CHEL</t>
+  </si>
+  <si>
+    <t>DDM SAMAR</t>
+  </si>
+  <si>
+    <t>DDM UL</t>
+  </si>
+  <si>
+    <t>DDM ORENB</t>
+  </si>
+  <si>
+    <t>DDM KURG</t>
+  </si>
+  <si>
+    <t>DDM SURGUT</t>
+  </si>
+  <si>
+    <t>DDM SVERDLOVSK</t>
+  </si>
+  <si>
+    <t>DDM TUMENSK</t>
+  </si>
+  <si>
+    <t>DDM OMSK</t>
+  </si>
+  <si>
+    <t>DDM NOVOSIB</t>
+  </si>
+  <si>
+    <t>DDM ALT</t>
+  </si>
+  <si>
+    <t>DDM REALT</t>
+  </si>
+  <si>
+    <t>DDM TOMSK</t>
+  </si>
+  <si>
+    <t>DDM KEMER</t>
+  </si>
+  <si>
+    <t>DDM NOVOK</t>
+  </si>
+  <si>
+    <t>DDM KRASN</t>
+  </si>
+  <si>
+    <t>DDM XAKAS</t>
+  </si>
+  <si>
+    <t>DDM TIVA</t>
+  </si>
+  <si>
+    <t>DDM BRYANSK</t>
+  </si>
+  <si>
+    <t>DDM ORLOVSK</t>
+  </si>
+  <si>
+    <t>DDM KURSK</t>
+  </si>
+  <si>
+    <t>DDM BELGOROD</t>
+  </si>
+  <si>
+    <t>DDM VORONESH</t>
+  </si>
+  <si>
+    <t>DDM LIPERSK</t>
+  </si>
+  <si>
+    <t>DDM TAMBOVSK</t>
+  </si>
+  <si>
+    <t>TDM Moscow</t>
+  </si>
+  <si>
+    <t>KADL Moscow</t>
   </si>
 </sst>
 </file>
@@ -1919,7 +2166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
@@ -2380,6 +2627,118 @@
       </c>
       <c r="E19" s="1" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2962,6 +3321,20 @@
       <c r="Y11" s="42"/>
       <c r="Z11" s="42"/>
       <c r="AA11" s="44"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -3039,7 +3412,7 @@
         <v>72</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>72</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -3053,7 +3426,7 @@
         <v>75</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>76</v>
@@ -3077,7 +3450,7 @@
         <v>75</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>79</v>
@@ -3099,7 +3472,7 @@
         <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>81</v>
@@ -3123,7 +3496,7 @@
         <v>80</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>84</v>
@@ -3145,7 +3518,7 @@
         <v>75</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>99</v>
+        <v>329</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>76</v>
@@ -3167,7 +3540,7 @@
         <v>75</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>99</v>
+        <v>330</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>87</v>
@@ -3189,7 +3562,7 @@
         <v>75</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>99</v>
+        <v>331</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>76</v>
@@ -3211,7 +3584,7 @@
         <v>75</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>99</v>
+        <v>332</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>87</v>
@@ -3233,7 +3606,7 @@
         <v>75</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>99</v>
+        <v>333</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>87</v>
@@ -3255,7 +3628,7 @@
         <v>75</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>99</v>
+        <v>334</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>92</v>
@@ -3277,7 +3650,7 @@
         <v>75</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>99</v>
+        <v>335</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>92</v>
@@ -3299,7 +3672,7 @@
         <v>75</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>99</v>
+        <v>336</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>92</v>
@@ -3321,7 +3694,7 @@
         <v>75</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>99</v>
+        <v>337</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>92</v>
@@ -3343,7 +3716,7 @@
         <v>98</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>99</v>
+        <v>338</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>100</v>
@@ -3365,7 +3738,7 @@
         <v>98</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>99</v>
+        <v>338</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>102</v>
@@ -3387,7 +3760,7 @@
         <v>98</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
+        <v>338</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>103</v>
@@ -3409,7 +3782,7 @@
         <v>98</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>99</v>
+        <v>339</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>103</v>
@@ -3431,7 +3804,7 @@
         <v>98</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>99</v>
+        <v>340</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>103</v>
@@ -3453,7 +3826,7 @@
         <v>98</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>99</v>
+        <v>341</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>102</v>
@@ -3475,7 +3848,7 @@
         <v>98</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>99</v>
+        <v>342</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>100</v>
@@ -3497,7 +3870,7 @@
         <v>98</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>99</v>
+        <v>343</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>109</v>
@@ -3519,7 +3892,7 @@
         <v>112</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>99</v>
+        <v>344</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>113</v>
@@ -3541,7 +3914,7 @@
         <v>112</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>99</v>
+        <v>345</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>113</v>
@@ -3563,7 +3936,7 @@
         <v>112</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>99</v>
+        <v>346</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>113</v>
@@ -3585,7 +3958,7 @@
         <v>112</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>99</v>
+        <v>347</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3607,7 +3980,7 @@
         <v>112</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>99</v>
+        <v>348</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>120</v>
@@ -3629,7 +4002,7 @@
         <v>112</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>99</v>
+        <v>349</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>120</v>
@@ -3651,7 +4024,7 @@
         <v>112</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>99</v>
+        <v>350</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>120</v>
@@ -3673,7 +4046,7 @@
         <v>112</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>99</v>
+        <v>351</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3695,7 +4068,7 @@
         <v>112</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>99</v>
+        <v>352</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>125</v>
@@ -3717,7 +4090,7 @@
         <v>129</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>130</v>
@@ -3739,7 +4112,7 @@
         <v>129</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>99</v>
+        <v>353</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>130</v>
@@ -3761,7 +4134,7 @@
         <v>129</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>99</v>
+        <v>354</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3783,7 +4156,7 @@
         <v>129</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>99</v>
+        <v>355</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>136</v>
@@ -3805,7 +4178,7 @@
         <v>129</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>99</v>
+        <v>356</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>138</v>
@@ -3827,7 +4200,7 @@
         <v>129</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>99</v>
+        <v>356</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>138</v>
@@ -3849,7 +4222,7 @@
         <v>139</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>99</v>
+        <v>356</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3871,7 +4244,7 @@
         <v>139</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>99</v>
+        <v>356</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>140</v>
@@ -3893,7 +4266,7 @@
         <v>142</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>143</v>
@@ -3915,7 +4288,7 @@
         <v>142</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>143</v>
@@ -3937,7 +4310,7 @@
         <v>142</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>144</v>
@@ -3959,7 +4332,7 @@
         <v>142</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>99</v>
+        <v>358</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>143</v>
@@ -3981,7 +4354,7 @@
         <v>142</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>99</v>
+        <v>359</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>147</v>
@@ -4003,7 +4376,7 @@
         <v>142</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>99</v>
+        <v>360</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>150</v>
@@ -4025,7 +4398,7 @@
         <v>152</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>99</v>
+        <v>361</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4047,7 +4420,7 @@
         <v>152</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>99</v>
+        <v>362</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>156</v>
@@ -4069,7 +4442,7 @@
         <v>152</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>99</v>
+        <v>362</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>157</v>
@@ -4091,7 +4464,7 @@
         <v>152</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>156</v>
@@ -4113,7 +4486,7 @@
         <v>152</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>157</v>
@@ -4135,7 +4508,7 @@
         <v>152</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>159</v>
@@ -4157,7 +4530,7 @@
         <v>162</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>163</v>
@@ -4179,7 +4552,7 @@
         <v>162</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>166</v>
@@ -4201,7 +4574,7 @@
         <v>162</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>99</v>
+        <v>366</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>169</v>
@@ -4223,7 +4596,7 @@
         <v>162</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>169</v>
@@ -4245,7 +4618,7 @@
         <v>162</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>99</v>
+        <v>368</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>172</v>
@@ -4267,7 +4640,7 @@
         <v>162</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>99</v>
+        <v>369</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>174</v>
@@ -4289,7 +4662,7 @@
         <v>162</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>174</v>
@@ -4311,7 +4684,7 @@
         <v>177</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>99</v>
+        <v>371</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>178</v>
@@ -4333,7 +4706,7 @@
         <v>180</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>99</v>
+        <v>372</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>181</v>
@@ -4355,7 +4728,7 @@
         <v>183</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>99</v>
+        <v>373</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>184</v>
@@ -4377,7 +4750,7 @@
         <v>183</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>99</v>
+        <v>374</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>187</v>
@@ -4399,7 +4772,7 @@
         <v>183</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>99</v>
+        <v>375</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>189</v>
@@ -4421,7 +4794,7 @@
         <v>192</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>99</v>
+        <v>376</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>193</v>
@@ -4443,7 +4816,7 @@
         <v>192</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>99</v>
+        <v>377</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>196</v>
@@ -4465,7 +4838,7 @@
         <v>192</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>99</v>
+        <v>378</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>199</v>
@@ -4487,7 +4860,7 @@
         <v>192</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>99</v>
+        <v>379</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>199</v>
@@ -4509,7 +4882,7 @@
         <v>192</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>99</v>
+        <v>380</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>193</v>
@@ -4531,7 +4904,7 @@
         <v>192</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>99</v>
+        <v>381</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>193</v>
@@ -4553,7 +4926,7 @@
         <v>192</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>99</v>
+        <v>382</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>193</v>
@@ -4575,7 +4948,7 @@
         <v>192</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>99</v>
+        <v>383</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>205</v>
@@ -4597,7 +4970,7 @@
         <v>192</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>99</v>
+        <v>384</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>205</v>
@@ -4619,7 +4992,7 @@
         <v>192</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>99</v>
+        <v>385</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>205</v>
@@ -4641,7 +5014,7 @@
         <v>211</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>99</v>
+        <v>386</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>212</v>
@@ -4663,7 +5036,7 @@
         <v>211</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>99</v>
+        <v>387</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>212</v>
@@ -4685,7 +5058,7 @@
         <v>211</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>99</v>
+        <v>388</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>212</v>
@@ -4707,7 +5080,7 @@
         <v>211</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>99</v>
+        <v>389</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>212</v>
@@ -4729,7 +5102,7 @@
         <v>211</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>99</v>
+        <v>390</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>212</v>
@@ -4751,7 +5124,7 @@
         <v>211</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>99</v>
+        <v>390</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>218</v>
@@ -4773,7 +5146,7 @@
         <v>211</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>99</v>
+        <v>391</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>218</v>
@@ -4795,7 +5168,7 @@
         <v>211</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>99</v>
+        <v>392</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>218</v>

--- a/Модель покрытия.xlsx
+++ b/Модель покрытия.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programs\MARSIntMap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\OneDrive\Desktop\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD44CD54-76BA-4E40-805C-7D0A678E2E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BB8162-AF88-4831-A08C-BC49F4FC433C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Исходник" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вариант 2'!$A$3:$AB$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Распределение TSL'!$A$1:$I$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Распределение TSL'!$A$1:$I$102</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="466">
   <si>
     <t>District</t>
   </si>
@@ -387,9 +387,6 @@
     <t>Продажи RKA c SO</t>
   </si>
   <si>
-    <t>Написать список сетей NA, D-com и тд, которые не нужно учитывать</t>
-  </si>
-  <si>
     <t>Регион</t>
   </si>
   <si>
@@ -1260,9 +1257,6 @@
     <t>DDM PRIMORSK</t>
   </si>
   <si>
-    <t>DDM PRMORSK</t>
-  </si>
-  <si>
     <t>DDM XABAR</t>
   </si>
   <si>
@@ -1375,6 +1369,225 @@
   </si>
   <si>
     <t>KADL Moscow</t>
+  </si>
+  <si>
+    <t>Фуд-трейд тест</t>
+  </si>
+  <si>
+    <t>Фуд-трейд тест 2</t>
+  </si>
+  <si>
+    <t>DDM Moscow 2</t>
+  </si>
+  <si>
+    <t>TSL Moscow 2</t>
+  </si>
+  <si>
+    <t>TSL TUL</t>
+  </si>
+  <si>
+    <t>TSL RYAZ</t>
+  </si>
+  <si>
+    <t>TSL KALYJ</t>
+  </si>
+  <si>
+    <t>TSL Nish</t>
+  </si>
+  <si>
+    <t>TSL Vladim</t>
+  </si>
+  <si>
+    <t>TSL Chyvash</t>
+  </si>
+  <si>
+    <t>TSL Kirov</t>
+  </si>
+  <si>
+    <t>TSL MARIYEL</t>
+  </si>
+  <si>
+    <t>TSL MORD</t>
+  </si>
+  <si>
+    <t>TSL PITER</t>
+  </si>
+  <si>
+    <t>TSL MURM</t>
+  </si>
+  <si>
+    <t>TSL NOVG</t>
+  </si>
+  <si>
+    <t>TSL KAREL</t>
+  </si>
+  <si>
+    <t>TSL PSKOV</t>
+  </si>
+  <si>
+    <t>TSL KALINING</t>
+  </si>
+  <si>
+    <t>TSL KOMI</t>
+  </si>
+  <si>
+    <t>TSL NENEC</t>
+  </si>
+  <si>
+    <t>TSL VOLOGOD</t>
+  </si>
+  <si>
+    <t>TSL ARHANG</t>
+  </si>
+  <si>
+    <t>TSL YAROSL</t>
+  </si>
+  <si>
+    <t>TSL KOSTROM</t>
+  </si>
+  <si>
+    <t>TSL TVER</t>
+  </si>
+  <si>
+    <t>TSL IVAN</t>
+  </si>
+  <si>
+    <t>TSL SMOLENSK</t>
+  </si>
+  <si>
+    <t>TSL Kamchatka</t>
+  </si>
+  <si>
+    <t>TSL SAXAL</t>
+  </si>
+  <si>
+    <t>TSL MAGADAN</t>
+  </si>
+  <si>
+    <t>TSL PRIMORSK</t>
+  </si>
+  <si>
+    <t>TSL XABAR</t>
+  </si>
+  <si>
+    <t>TSL EVREY</t>
+  </si>
+  <si>
+    <t>TSL YAKUT</t>
+  </si>
+  <si>
+    <t>TSL AMUR</t>
+  </si>
+  <si>
+    <t>TSL SABAYK</t>
+  </si>
+  <si>
+    <t>TSL BYRAT</t>
+  </si>
+  <si>
+    <t>TSL IRKUTSK</t>
+  </si>
+  <si>
+    <t>TSL TATAR</t>
+  </si>
+  <si>
+    <t>TSL BASHK</t>
+  </si>
+  <si>
+    <t>TSL UDMU</t>
+  </si>
+  <si>
+    <t>TSL PERM</t>
+  </si>
+  <si>
+    <t>TSL CHEL</t>
+  </si>
+  <si>
+    <t>TSL SAMAR</t>
+  </si>
+  <si>
+    <t>TSL UL</t>
+  </si>
+  <si>
+    <t>TSL ORENB</t>
+  </si>
+  <si>
+    <t>TSL KURG</t>
+  </si>
+  <si>
+    <t>TSL SURGUT</t>
+  </si>
+  <si>
+    <t>TSL SVERDLOVSK</t>
+  </si>
+  <si>
+    <t>TSL TUMENSK</t>
+  </si>
+  <si>
+    <t>TSL OMSK</t>
+  </si>
+  <si>
+    <t>TSL NOVOSIB</t>
+  </si>
+  <si>
+    <t>TSL ALT</t>
+  </si>
+  <si>
+    <t>TSL REALT</t>
+  </si>
+  <si>
+    <t>TSL TOMSK</t>
+  </si>
+  <si>
+    <t>TSL KEMER</t>
+  </si>
+  <si>
+    <t>TSL NOVOK</t>
+  </si>
+  <si>
+    <t>TSL KRASN</t>
+  </si>
+  <si>
+    <t>TSL XAKAS</t>
+  </si>
+  <si>
+    <t>TSL TIVA</t>
+  </si>
+  <si>
+    <t>TSL BRYANSK</t>
+  </si>
+  <si>
+    <t>TSL ORLOVSK</t>
+  </si>
+  <si>
+    <t>TSL KURSK</t>
+  </si>
+  <si>
+    <t>TSL BELGOROD</t>
+  </si>
+  <si>
+    <t>TSL VORONESH</t>
+  </si>
+  <si>
+    <t>TSL LIPERSK</t>
+  </si>
+  <si>
+    <t>TSL TAMBOVSK</t>
+  </si>
+  <si>
+    <t>TSL North</t>
+  </si>
+  <si>
+    <t>RADM Moscow 2</t>
+  </si>
+  <si>
+    <t>RAE Spar 3</t>
+  </si>
+  <si>
+    <t>RAE SPPP</t>
+  </si>
+  <si>
+    <t>TSL Moscow 3</t>
   </si>
 </sst>
 </file>
@@ -1888,7 +2101,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2167,22 +2380,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="5" width="18.109375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="11.33203125" style="2" customWidth="1"/>
-    <col min="8" max="14" width="11.33203125" style="1" customWidth="1"/>
-    <col min="15" max="17" width="10.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="18.140625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="11.28515625" style="2" customWidth="1"/>
+    <col min="8" max="14" width="11.28515625" style="1" customWidth="1"/>
+    <col min="15" max="17" width="10.7109375" style="1" customWidth="1"/>
     <col min="18" max="18" width="12" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.88671875" style="1"/>
+    <col min="19" max="19" width="10.7109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2244,7 +2457,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -2286,7 +2499,7 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -2324,7 +2537,7 @@
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -2361,7 +2574,7 @@
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -2392,7 +2605,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -2432,7 +2645,7 @@
       </c>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
@@ -2469,7 +2682,7 @@
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -2503,7 +2716,7 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -2531,48 +2744,48 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -2580,7 +2793,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2591,15 +2804,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -2607,138 +2820,138 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>302</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C24" s="1" t="s">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C25" s="1" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D26" s="1" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2750,22 +2963,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62F99B76-7CBC-45E3-87BE-CFF232B038A4}">
   <dimension ref="A1:AB20"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="5" width="18.109375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="11.33203125" style="2" customWidth="1"/>
-    <col min="8" max="21" width="11.33203125" style="1" customWidth="1"/>
-    <col min="22" max="24" width="10.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="18.140625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="11.28515625" style="2" customWidth="1"/>
+    <col min="8" max="21" width="11.28515625" style="1" customWidth="1"/>
+    <col min="22" max="24" width="10.7109375" style="1" customWidth="1"/>
     <col min="25" max="25" width="12" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="11.6640625" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.88671875" style="1"/>
+    <col min="26" max="26" width="10.7109375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="11.7109375" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2793,7 +3006,7 @@
       <c r="Z1" s="51"/>
       <c r="AA1" s="52"/>
     </row>
-    <row r="2" spans="1:28" s="8" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" s="8" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I2" s="53" t="s">
         <v>48</v>
       </c>
@@ -2834,7 +3047,7 @@
       <c r="Z2" s="12"/>
       <c r="AA2" s="13"/>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -2917,7 +3130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>20</v>
       </c>
@@ -2970,7 +3183,7 @@
       <c r="Z4" s="28"/>
       <c r="AA4" s="29"/>
     </row>
-    <row r="5" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>20</v>
       </c>
@@ -3017,7 +3230,7 @@
       <c r="Z5" s="36"/>
       <c r="AA5" s="38"/>
     </row>
-    <row r="6" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>20</v>
       </c>
@@ -3062,7 +3275,7 @@
       <c r="Z6" s="36"/>
       <c r="AA6" s="38"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>20</v>
       </c>
@@ -3120,7 +3333,7 @@
       <c r="AA7" s="32"/>
       <c r="AB7"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
         <v>35</v>
       </c>
@@ -3173,7 +3386,7 @@
       <c r="Z8" s="30"/>
       <c r="AA8" s="32"/>
     </row>
-    <row r="9" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>35</v>
       </c>
@@ -3220,7 +3433,7 @@
       <c r="Z9" s="36"/>
       <c r="AA9" s="38"/>
     </row>
-    <row r="10" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>35</v>
       </c>
@@ -3265,7 +3478,7 @@
       <c r="Z10" s="36"/>
       <c r="AA10" s="38"/>
     </row>
-    <row r="11" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="42" t="s">
         <v>35</v>
       </c>
@@ -3322,46 +3535,69 @@
       <c r="Z11" s="42"/>
       <c r="AA11" s="44"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="K16"/>
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17"/>
       <c r="K17"/>
       <c r="L17"/>
       <c r="M17"/>
       <c r="V17"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20"/>
     </row>
   </sheetData>
@@ -3379,2226 +3615,2475 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}">
-  <dimension ref="A1:H100"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H102"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="4" width="26.5546875" customWidth="1"/>
-    <col min="5" max="6" width="26.6640625" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="2" max="4" width="26.5703125" customWidth="1"/>
+    <col min="5" max="6" width="26.7109375" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="D4" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="D6" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H59" s="6"/>
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H60" s="6"/>
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H61" s="6"/>
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H62" s="6"/>
+    </row>
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H65" s="6"/>
+    </row>
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H66" s="6"/>
+    </row>
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H67" s="6"/>
+    </row>
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H68" s="6"/>
+    </row>
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H69" s="6"/>
+    </row>
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H70" s="6"/>
+    </row>
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H71" s="6"/>
+    </row>
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H72" s="6"/>
+    </row>
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H73" s="6"/>
+    </row>
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H74" s="6"/>
+    </row>
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H75" s="6"/>
+    </row>
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H76" s="6"/>
+    </row>
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H77" s="6"/>
+    </row>
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H78" s="6"/>
+    </row>
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H79" s="6"/>
+    </row>
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H80" s="6"/>
+    </row>
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H81" s="6"/>
+    </row>
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H82" s="6"/>
+    </row>
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H83" s="6"/>
+    </row>
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H84" s="6"/>
+    </row>
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H85" s="6"/>
+    </row>
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H86" s="6"/>
+    </row>
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H87" s="6"/>
+    </row>
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H88" s="6"/>
+    </row>
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H89" s="6"/>
+    </row>
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H90" s="6"/>
+    </row>
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H91" s="6"/>
+    </row>
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H92" s="6"/>
+    </row>
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H93" s="6"/>
+    </row>
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H94" s="6"/>
+    </row>
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H95" s="6"/>
+    </row>
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H96" s="6"/>
+    </row>
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H97" s="6"/>
+    </row>
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H98" s="6"/>
+    </row>
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H99" s="6"/>
+    </row>
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H100" s="6"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D101" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="E101" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="F101" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C102" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D102" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="E102" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F102" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H45" s="6"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H46" s="6"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H51" s="6"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H53" s="6"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H55" s="6"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H67" s="6"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="H68" s="6"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="H69" s="6"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="H70" s="6"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="H71" s="6"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="H72" s="6"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="H73" s="6"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H74" s="6"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H75" s="6"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H76" s="6"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H77" s="6"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H78" s="6"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H79" s="6"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H80" s="6"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H81" s="6"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H82" s="6"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H83" s="6"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H84" s="6"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="H85" s="6"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H86" s="6"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H87" s="6"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H88" s="6"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H89" s="6"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H90" s="6"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H91" s="6"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="H92" s="6"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="H93" s="6"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H94" s="6"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H95" s="6"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H96" s="6"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="H97" s="6"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="H98" s="6"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="H99" s="6"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="H100" s="6"/>
+      <c r="G102" s="6" t="s">
+        <v>394</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I100" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}"/>
+  <autoFilter ref="A1:I102" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Москва и МО"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5607,514 +6092,514 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34489A3-A8B0-4D6F-A6E8-B4FAFCF5D4F6}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>253</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>254</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>253</v>
-      </c>
       <c r="D3" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>253</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>253</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="D13" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G13" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G15" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>283</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G17" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>281</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>281</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>281</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>281</v>
-      </c>
       <c r="D23" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -6123,7 +6608,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -6132,7 +6617,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -6141,7 +6626,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -6150,7 +6635,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -6159,7 +6644,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -6176,7 +6661,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F033FB-4DB8-4067-A8C0-4DACAF03F6E6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Модель покрытия.xlsx
+++ b/Модель покрытия.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\OneDrive\Desktop\MARSIntMap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BB8162-AF88-4831-A08C-BC49F4FC433C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A0C86B-B770-41E3-8F17-7671813BB1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,6 +36,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3615,7 +3618,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3750,7 +3752,7 @@
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
@@ -3774,7 +3776,7 @@
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>72</v>
       </c>
@@ -3798,7 +3800,7 @@
       </c>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>72</v>
       </c>
@@ -3822,7 +3824,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>72</v>
       </c>
@@ -3846,7 +3848,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>72</v>
       </c>
@@ -3870,7 +3872,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>72</v>
       </c>
@@ -3894,7 +3896,7 @@
       </c>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>72</v>
       </c>
@@ -3918,7 +3920,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>72</v>
       </c>
@@ -3942,7 +3944,7 @@
       </c>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>72</v>
       </c>
@@ -3966,7 +3968,7 @@
       </c>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>95</v>
       </c>
@@ -3990,7 +3992,7 @@
       </c>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>95</v>
       </c>
@@ -4014,7 +4016,7 @@
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>95</v>
       </c>
@@ -4038,7 +4040,7 @@
       </c>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>95</v>
       </c>
@@ -4062,7 +4064,7 @@
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>95</v>
       </c>
@@ -4086,7 +4088,7 @@
       </c>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>95</v>
       </c>
@@ -4110,7 +4112,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>95</v>
       </c>
@@ -4134,7 +4136,7 @@
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>95</v>
       </c>
@@ -4158,7 +4160,7 @@
       </c>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>95</v>
       </c>
@@ -4182,7 +4184,7 @@
       </c>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>95</v>
       </c>
@@ -4206,7 +4208,7 @@
       </c>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>95</v>
       </c>
@@ -4230,7 +4232,7 @@
       </c>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>95</v>
       </c>
@@ -4254,7 +4256,7 @@
       </c>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>95</v>
       </c>
@@ -4278,7 +4280,7 @@
       </c>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>95</v>
       </c>
@@ -4302,7 +4304,7 @@
       </c>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>95</v>
       </c>
@@ -4326,7 +4328,7 @@
       </c>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>95</v>
       </c>
@@ -4350,7 +4352,7 @@
       </c>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>95</v>
       </c>
@@ -4374,7 +4376,7 @@
       </c>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>126</v>
       </c>
@@ -4398,7 +4400,7 @@
       </c>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>126</v>
       </c>
@@ -4422,7 +4424,7 @@
       </c>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>126</v>
       </c>
@@ -4446,7 +4448,7 @@
       </c>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>126</v>
       </c>
@@ -4470,7 +4472,7 @@
       </c>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>126</v>
       </c>
@@ -4494,7 +4496,7 @@
       </c>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>126</v>
       </c>
@@ -4518,7 +4520,7 @@
       </c>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>126</v>
       </c>
@@ -4542,7 +4544,7 @@
       </c>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>126</v>
       </c>
@@ -4566,7 +4568,7 @@
       </c>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>126</v>
       </c>
@@ -4590,7 +4592,7 @@
       </c>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>126</v>
       </c>
@@ -4614,7 +4616,7 @@
       </c>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>126</v>
       </c>
@@ -4638,7 +4640,7 @@
       </c>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>126</v>
       </c>
@@ -4662,7 +4664,7 @@
       </c>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>126</v>
       </c>
@@ -4686,7 +4688,7 @@
       </c>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>126</v>
       </c>
@@ -4710,7 +4712,7 @@
       </c>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>126</v>
       </c>
@@ -4734,7 +4736,7 @@
       </c>
       <c r="H46" s="6"/>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>126</v>
       </c>
@@ -4758,7 +4760,7 @@
       </c>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>126</v>
       </c>
@@ -4782,7 +4784,7 @@
       </c>
       <c r="H48" s="6"/>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>126</v>
       </c>
@@ -4806,7 +4808,7 @@
       </c>
       <c r="H49" s="6"/>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>126</v>
       </c>
@@ -4830,7 +4832,7 @@
       </c>
       <c r="H50" s="6"/>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>126</v>
       </c>
@@ -4854,7 +4856,7 @@
       </c>
       <c r="H51" s="6"/>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>159</v>
       </c>
@@ -4878,7 +4880,7 @@
       </c>
       <c r="H52" s="6"/>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>159</v>
       </c>
@@ -4902,7 +4904,7 @@
       </c>
       <c r="H53" s="6"/>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>159</v>
       </c>
@@ -4926,7 +4928,7 @@
       </c>
       <c r="H54" s="6"/>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>159</v>
       </c>
@@ -4950,7 +4952,7 @@
       </c>
       <c r="H55" s="6"/>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>159</v>
       </c>
@@ -4974,7 +4976,7 @@
       </c>
       <c r="H56" s="6"/>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>159</v>
       </c>
@@ -4998,7 +5000,7 @@
       </c>
       <c r="H57" s="6"/>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>159</v>
       </c>
@@ -5022,7 +5024,7 @@
       </c>
       <c r="H58" s="6"/>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>159</v>
       </c>
@@ -5046,7 +5048,7 @@
       </c>
       <c r="H59" s="6"/>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>159</v>
       </c>
@@ -5070,7 +5072,7 @@
       </c>
       <c r="H60" s="6"/>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>159</v>
       </c>
@@ -5094,7 +5096,7 @@
       </c>
       <c r="H61" s="6"/>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>159</v>
       </c>
@@ -5118,7 +5120,7 @@
       </c>
       <c r="H62" s="6"/>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>159</v>
       </c>
@@ -5142,7 +5144,7 @@
       </c>
       <c r="H63" s="6"/>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>189</v>
       </c>
@@ -5166,7 +5168,7 @@
       </c>
       <c r="H64" s="6"/>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>189</v>
       </c>
@@ -5190,7 +5192,7 @@
       </c>
       <c r="H65" s="6"/>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>189</v>
       </c>
@@ -5214,7 +5216,7 @@
       </c>
       <c r="H66" s="6"/>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>189</v>
       </c>
@@ -5238,7 +5240,7 @@
       </c>
       <c r="H67" s="6"/>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>189</v>
       </c>
@@ -5262,7 +5264,7 @@
       </c>
       <c r="H68" s="6"/>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>189</v>
       </c>
@@ -5286,7 +5288,7 @@
       </c>
       <c r="H69" s="6"/>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>189</v>
       </c>
@@ -5310,7 +5312,7 @@
       </c>
       <c r="H70" s="6"/>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>189</v>
       </c>
@@ -5334,7 +5336,7 @@
       </c>
       <c r="H71" s="6"/>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>189</v>
       </c>
@@ -5358,7 +5360,7 @@
       </c>
       <c r="H72" s="6"/>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>189</v>
       </c>
@@ -5382,7 +5384,7 @@
       </c>
       <c r="H73" s="6"/>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>208</v>
       </c>
@@ -5406,7 +5408,7 @@
       </c>
       <c r="H74" s="6"/>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>208</v>
       </c>
@@ -5430,7 +5432,7 @@
       </c>
       <c r="H75" s="6"/>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>208</v>
       </c>
@@ -5454,7 +5456,7 @@
       </c>
       <c r="H76" s="6"/>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>208</v>
       </c>
@@ -5478,7 +5480,7 @@
       </c>
       <c r="H77" s="6"/>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>208</v>
       </c>
@@ -5502,7 +5504,7 @@
       </c>
       <c r="H78" s="6"/>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>208</v>
       </c>
@@ -5526,7 +5528,7 @@
       </c>
       <c r="H79" s="6"/>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>208</v>
       </c>
@@ -5550,7 +5552,7 @@
       </c>
       <c r="H80" s="6"/>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>208</v>
       </c>
@@ -5574,7 +5576,7 @@
       </c>
       <c r="H81" s="6"/>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>208</v>
       </c>
@@ -5598,7 +5600,7 @@
       </c>
       <c r="H82" s="6"/>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>208</v>
       </c>
@@ -5622,7 +5624,7 @@
       </c>
       <c r="H83" s="6"/>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>208</v>
       </c>
@@ -5646,7 +5648,7 @@
       </c>
       <c r="H84" s="6"/>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>208</v>
       </c>
@@ -5670,7 +5672,7 @@
       </c>
       <c r="H85" s="6"/>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>208</v>
       </c>
@@ -5694,7 +5696,7 @@
       </c>
       <c r="H86" s="6"/>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>208</v>
       </c>
@@ -5718,7 +5720,7 @@
       </c>
       <c r="H87" s="6"/>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>208</v>
       </c>
@@ -5742,7 +5744,7 @@
       </c>
       <c r="H88" s="6"/>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>208</v>
       </c>
@@ -5766,7 +5768,7 @@
       </c>
       <c r="H89" s="6"/>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>208</v>
       </c>
@@ -5790,7 +5792,7 @@
       </c>
       <c r="H90" s="6"/>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>208</v>
       </c>
@@ -5814,7 +5816,7 @@
       </c>
       <c r="H91" s="6"/>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>208</v>
       </c>
@@ -5838,7 +5840,7 @@
       </c>
       <c r="H92" s="6"/>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>208</v>
       </c>
@@ -5862,7 +5864,7 @@
       </c>
       <c r="H93" s="6"/>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>208</v>
       </c>
@@ -5886,7 +5888,7 @@
       </c>
       <c r="H94" s="6"/>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>208</v>
       </c>
@@ -5910,7 +5912,7 @@
       </c>
       <c r="H95" s="6"/>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>208</v>
       </c>
@@ -5934,7 +5936,7 @@
       </c>
       <c r="H96" s="6"/>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>208</v>
       </c>
@@ -5958,7 +5960,7 @@
       </c>
       <c r="H97" s="6"/>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>208</v>
       </c>
@@ -5982,7 +5984,7 @@
       </c>
       <c r="H98" s="6"/>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>208</v>
       </c>
@@ -6006,7 +6008,7 @@
       </c>
       <c r="H99" s="6"/>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>208</v>
       </c>
@@ -6077,13 +6079,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I102" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Москва и МО"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I102" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Модель покрытия.xlsx
+++ b/Модель покрытия.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A0C86B-B770-41E3-8F17-7671813BB1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F1A313-763C-453C-98AE-8F5D8F177766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="463">
   <si>
     <t>District</t>
   </si>
@@ -438,9 +438,6 @@
     <t>Беспятых Ваня</t>
   </si>
   <si>
-    <t>Фуд-трейд</t>
-  </si>
-  <si>
     <t>Сорсо (закрываем)</t>
   </si>
   <si>
@@ -1372,12 +1369,6 @@
   </si>
   <si>
     <t>KADL Moscow</t>
-  </si>
-  <si>
-    <t>Фуд-трейд тест</t>
-  </si>
-  <si>
-    <t>Фуд-трейд тест 2</t>
   </si>
   <si>
     <t>DDM Moscow 2</t>
@@ -2749,38 +2740,38 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2809,10 +2800,10 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2825,136 +2816,136 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C22" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -3546,10 +3537,10 @@
         <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
@@ -3563,7 +3554,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
@@ -3574,10 +3565,10 @@
         <v>21</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
@@ -3651,7 +3642,7 @@
         <v>71</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3713,19 +3704,19 @@
         <v>79</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3739,16 +3730,16 @@
         <v>79</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="H5" s="6"/>
     </row>
@@ -3757,19 +3748,19 @@
         <v>72</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>77</v>
@@ -3781,19 +3772,19 @@
         <v>72</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>77</v>
@@ -3805,19 +3796,19 @@
         <v>72</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>77</v>
@@ -3829,19 +3820,19 @@
         <v>72</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>77</v>
@@ -3853,19 +3844,19 @@
         <v>72</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>77</v>
@@ -3877,19 +3868,19 @@
         <v>72</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>77</v>
@@ -3901,19 +3892,19 @@
         <v>72</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>77</v>
@@ -3925,19 +3916,19 @@
         <v>72</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>77</v>
@@ -3949,19 +3940,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>77</v>
@@ -3970,2113 +3961,2085 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D16" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="F22" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="F26" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E29" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="F30" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="D32" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="F32" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="F33" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="F34" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>139</v>
-      </c>
       <c r="F38" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>139</v>
-      </c>
       <c r="F39" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="D40" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="F40" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="F41" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="D42" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="F43" s="6" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="F44" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="F45" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H45" s="6"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="H46" s="6"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>155</v>
-      </c>
       <c r="F47" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H49" s="6"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H50" s="6"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="F51" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H51" s="6"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="D52" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="H52" s="6"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="F53" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="G53" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="H53" s="6"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>168</v>
-      </c>
       <c r="F54" s="6" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H54" s="6"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H55" s="6"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B56" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>171</v>
-      </c>
       <c r="F56" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H56" s="6"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>173</v>
-      </c>
       <c r="F57" s="6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H57" s="6"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H58" s="6"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B59" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="D59" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>177</v>
-      </c>
       <c r="F59" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H59" s="6"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B60" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="F60" s="6" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H60" s="6"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="D61" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E61" s="6" t="s">
+      <c r="F61" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G61" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B62" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>186</v>
-      </c>
       <c r="F62" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H62" s="6"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="F63" s="6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H63" s="6"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="D64" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="E64" s="6" t="s">
+      <c r="F64" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="H64" s="6"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B65" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E65" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E65" s="6" t="s">
+      <c r="F65" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="G65" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B66" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>198</v>
-      </c>
       <c r="F66" s="6" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H66" s="6"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C68" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="E68" s="6" t="s">
+      <c r="F68" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E69" s="6" t="s">
+      <c r="F69" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G69" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C70" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="E70" s="6" t="s">
+      <c r="F70" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B71" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="E71" s="6" t="s">
+      <c r="F71" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="G71" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E73" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G73" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="H73" s="6"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="C74" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="D74" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E74" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="E74" s="6" t="s">
+      <c r="F74" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="H74" s="6"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C75" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E75" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D75" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="E75" s="6" t="s">
+      <c r="F75" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="G75" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="H75" s="6"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C76" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D76" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="E76" s="6" t="s">
+      <c r="F76" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="G76" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="H76" s="6"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C77" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E77" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="E77" s="6" t="s">
+      <c r="F77" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="G77" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="H77" s="6"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C78" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D78" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>211</v>
-      </c>
       <c r="F78" s="6" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H78" s="6"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B79" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>217</v>
-      </c>
       <c r="F79" s="6" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H79" s="6"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H80" s="6"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H81" s="6"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E82" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="F82" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H82" s="6"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H83" s="6"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H84" s="6"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B85" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="D85" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E85" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E85" s="6" t="s">
+      <c r="F85" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G85" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="H85" s="6"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B86" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>229</v>
-      </c>
       <c r="F86" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H87" s="6"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H88" s="6"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H89" s="6"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H90" s="6"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H91" s="6"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="D92" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E92" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E92" s="6" t="s">
+      <c r="F92" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G92" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B93" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G93" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C94" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E94" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D94" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>237</v>
-      </c>
       <c r="F94" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H94" s="6"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C95" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E95" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D95" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>237</v>
-      </c>
       <c r="F95" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H95" s="6"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H96" s="6"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B97" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E97" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>245</v>
-      </c>
       <c r="F97" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H97" s="6"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E98" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G98" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="H98" s="6"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E99" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G99" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="H99" s="6"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B100" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>249</v>
-      </c>
       <c r="F100" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H100" s="6"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>393</v>
-      </c>
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>394</v>
-      </c>
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I102" xr:uid="{A4AB1B0E-358B-42C2-9D0A-E02812A76C3C}"/>
@@ -6119,7 +6082,7 @@
         <v>71</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -6127,20 +6090,20 @@
         <v>72</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -6148,20 +6111,20 @@
         <v>72</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="D3" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6169,20 +6132,20 @@
         <v>72</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6190,20 +6153,20 @@
         <v>72</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6211,388 +6174,388 @@
         <v>72</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D13" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D14" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="D23" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
